--- a/Datas/Quest.xlsx
+++ b/Datas/Quest.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1100,7 +1100,9 @@
   <dimension ref="A1:G8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.25" outlineLevelRow="7" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="10" width="28.625" style="1" customWidth="1"/>
+    <col min="1" max="2" width="28.625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="48.625" style="1" customWidth="1"/>
+    <col min="4" max="10" width="28.625" style="1" customWidth="1"/>
     <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>

--- a/Datas/Quest.xlsx
+++ b/Datas/Quest.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="18">
   <si>
     <t>##var</t>
   </si>
@@ -40,16 +40,10 @@
     <t>QuestType</t>
   </si>
   <si>
-    <t>TargetRange</t>
-  </si>
-  <si>
-    <t>Duration</t>
-  </si>
-  <si>
-    <t>RewardRange</t>
-  </si>
-  <si>
-    <t>Comment</t>
+    <t>TargetValue</t>
+  </si>
+  <si>
+    <t>RewardValue</t>
   </si>
   <si>
     <t>##type</t>
@@ -61,15 +55,6 @@
     <t>HuntingConfig.Enum.EQuestType</t>
   </si>
   <si>
-    <t>(array#sep=,),int</t>
-  </si>
-  <si>
-    <t>float</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
     <t>##group</t>
   </si>
   <si>
@@ -85,49 +70,19 @@
     <t xml:space="preserve"> 任务类型</t>
   </si>
   <si>
-    <t>任务目标数值范围</t>
-  </si>
-  <si>
-    <t>任务持续时间</t>
-  </si>
-  <si>
-    <t>任务奖励数值范围</t>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>KillLargeAnimal</t>
-  </si>
-  <si>
-    <t>1,2</t>
-  </si>
-  <si>
-    <t>5,10</t>
-  </si>
-  <si>
-    <t>示例</t>
-  </si>
-  <si>
-    <t>CollectMeat</t>
-  </si>
-  <si>
-    <t>10,20</t>
-  </si>
-  <si>
-    <t>8,15</t>
-  </si>
-  <si>
-    <t>UsePaidItem</t>
-  </si>
-  <si>
-    <t>3,8</t>
-  </si>
-  <si>
-    <t>Settle</t>
-  </si>
-  <si>
-    <t>1,1</t>
+    <t>目标值</t>
+  </si>
+  <si>
+    <t>奖励值</t>
+  </si>
+  <si>
+    <t>Hunting</t>
+  </si>
+  <si>
+    <t>Collect</t>
+  </si>
+  <si>
+    <t>Consume</t>
   </si>
 </sst>
 </file>
@@ -1097,16 +1052,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.25" outlineLevelRow="7" outlineLevelCol="6"/>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.25" outlineLevelRow="6" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="2" width="28.625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="48.625" style="1" customWidth="1"/>
-    <col min="4" max="10" width="28.625" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="1"/>
+    <col min="3" max="3" width="36.625" style="1" customWidth="1"/>
+    <col min="4" max="8" width="28.625" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:7">
+    <row r="1" ht="28" customHeight="1" spans="1:5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1122,164 +1077,101 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+    </row>
+    <row r="2" ht="28" customHeight="1" spans="1:5">
+      <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="C2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="2" ht="28" customHeight="1" spans="1:7">
-      <c r="A2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="2" t="s">
+    <row r="3" ht="28" customHeight="1" spans="1:5">
+      <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="B3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1" spans="1:5">
+      <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="B4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="D4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="3" ht="28" customHeight="1" spans="1:7">
-      <c r="A3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1" spans="1:7">
-      <c r="A4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1" spans="1:7">
+    <row r="5" ht="28" customHeight="1" spans="1:5">
       <c r="A5" s="3"/>
       <c r="B5" s="3">
         <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="3">
-        <v>20</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>25</v>
+        <v>15</v>
+      </c>
+      <c r="D5" s="3">
+        <v>10</v>
+      </c>
+      <c r="E5" s="4">
+        <v>10</v>
       </c>
     </row>
-    <row r="6" ht="28" customHeight="1" spans="1:7">
+    <row r="6" ht="28" customHeight="1" spans="1:5">
       <c r="A6" s="3"/>
       <c r="B6" s="3">
         <v>2</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" s="3">
-        <v>20</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>25</v>
+        <v>16</v>
+      </c>
+      <c r="D6" s="3">
+        <v>50</v>
+      </c>
+      <c r="E6" s="4">
+        <v>10</v>
       </c>
     </row>
-    <row r="7" ht="28" customHeight="1" spans="1:7">
+    <row r="7" ht="28" customHeight="1" spans="1:5">
       <c r="A7" s="3"/>
       <c r="B7" s="3">
         <v>3</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" s="3">
-        <v>20</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" ht="28" customHeight="1" spans="1:7">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3">
-        <v>4</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8" s="3">
-        <v>20</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>25</v>
+        <v>17</v>
+      </c>
+      <c r="D7" s="3">
+        <v>1</v>
+      </c>
+      <c r="E7" s="4">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
